--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.79.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.79.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.79.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.79.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.79.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.79.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0079.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0079.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,24 +613,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�°</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+53F0 CJK UNIFIED IDEOGRAPH-53F0 | isolated marker/symbol line :: 台</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Order 65, are the words, 4â€˜ Without requiring an</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]72</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]72</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�°</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+53F0 CJK UNIFIED IDEOGRAPH-53F0 | isolated marker/symbol line :: 台</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]72</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,14 +676,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: above Order 66 of 1850, the subpo Ã¦ ena is directed to</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: be served on the Â« Plaintiffâ€�. The above 66th Order</t>
-        </is>
-      </c>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -687,7 +687,11 @@
           <t>L25: isolated marker/symbol line :: 72</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L89: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -723,7 +727,7 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å›�</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+56CD CJK UNIFIED IDEOGRAPH-56CD | isolated marker/symbol line :: 囍</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr"/>
@@ -731,7 +735,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: æ°”</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -754,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -903,7 +907,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å›�</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+56CD CJK UNIFIED IDEOGRAPH-56CD | isolated marker/symbol line :: 囍</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -970,7 +974,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1009,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
